--- a/ig/ch-elm/ValueSet-ch-elm-results-sal-org.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-sal-org.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>5595000</t>
   </si>
   <si>
-    <t>Salmonella Typhi (organism)</t>
+    <t>Salmonella Typhi</t>
   </si>
   <si>
     <t>1179072002</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-sal-org.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-sal-org.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-sal-org.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-sal-org.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-sal-org.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-sal-org.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
